--- a/data/Escenarios_DCH/Swap_variable_3estaciones/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Swap_variable_3estaciones/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Swap_variable_3estaciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_DCH\Swap_variable_3estaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220D901A-C0B7-4B1C-9E14-D8FB476C3040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBC16F6-B57F-4A2D-B521-91CBDF5DE68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2094,36 +2094,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="25" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="26" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="26" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="26" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="26" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="26" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>3</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>1</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34">
         <v>2</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>3</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>4</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>5</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>6</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>7</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>8</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>9</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>10</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>11</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" s="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>12</v>
       </c>
@@ -3453,9 +3453,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3465,13 +3465,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3610,12 +3610,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3704,16 +3704,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="43" t="s">
         <v>3</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51">
         <v>0</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53">
         <v>1</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51">
         <v>3</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>4</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53">
         <v>5</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51">
         <v>6</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="53">
         <v>7</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>8</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
         <v>9</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53">
         <v>10</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53">
         <v>11</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>12</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="51">
         <v>13</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53">
         <v>14</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>15</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>16</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>17</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53">
         <v>18</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>19</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>20</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>21</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>22</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="51">
         <v>23</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53">
         <v>24</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="51">
         <v>25</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>26</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>27</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="51">
         <v>28</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>29</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>30</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="51">
         <v>31</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="53">
         <v>32</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>33</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="51">
         <v>34</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>35</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>36</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>37</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="51">
         <v>38</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>39</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>40</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>41</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>42</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>43</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <v>44</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>45</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="53">
         <v>46</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>47</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <v>48</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>49</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>50</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>52</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>53</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <v>54</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>55</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>56</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>57</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="53">
         <v>58</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>59</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>60</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>61</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="53">
         <v>62</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="53">
         <v>63</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="53">
         <v>64</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="53">
         <v>65</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="53">
         <v>66</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="53">
         <v>67</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="53">
         <v>68</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="53">
         <v>69</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="53">
         <v>70</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="53">
         <v>71</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="53">
         <v>72</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="53">
         <v>73</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="53">
         <v>74</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="53">
         <v>75</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="53">
         <v>76</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="53">
         <v>77</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="53">
         <v>78</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>79</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>80</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>81</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>82</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>83</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>84</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>85</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="53">
         <v>86</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="53">
         <v>87</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="53">
         <v>88</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="53">
         <v>89</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="53">
         <v>90</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>91</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>92</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>93</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="53">
         <v>94</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="53">
         <v>95</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="53">
         <v>96</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="53">
         <v>97</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="53">
         <v>98</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="53">
         <v>99</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="53">
         <v>100</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="53">
         <v>101</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="53">
         <v>102</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="53">
         <v>103</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="53">
         <v>104</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="53">
         <v>105</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="53">
         <v>106</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="53">
         <v>107</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="53">
         <v>108</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="53">
         <v>109</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="53">
         <v>110</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="53">
         <v>111</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="53">
         <v>112</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="53">
         <v>113</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="53">
         <v>114</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="53">
         <v>115</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="53">
         <v>116</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="53">
         <v>117</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="53">
         <v>118</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="53">
         <v>119</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="53">
         <v>120</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="53">
         <v>121</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="53">
         <v>122</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="53">
         <v>123</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="53">
         <v>124</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="53">
         <v>125</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="53">
         <v>126</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="53">
         <v>127</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="53">
         <v>128</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="53">
         <v>129</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="53">
         <v>130</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="53">
         <v>131</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="53">
         <v>132</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="53">
         <v>133</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="53">
         <v>134</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="53">
         <v>135</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="53">
         <v>136</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="53">
         <v>137</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="53">
         <v>138</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="53">
         <v>139</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="53">
         <v>140</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="53">
         <v>141</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="53">
         <v>142</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="53">
         <v>143</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="53">
         <v>144</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="53">
         <v>145</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="53">
         <v>146</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="53">
         <v>147</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="53">
         <v>148</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="53">
         <v>149</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="53">
         <v>150</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="53">
         <v>151</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="53">
         <v>152</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="53">
         <v>153</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="53">
         <v>154</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="53">
         <v>155</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="53">
         <v>156</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="53">
         <v>157</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="53">
         <v>158</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="53">
         <v>159</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="53">
         <v>160</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="53">
         <v>161</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="53">
         <v>162</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="53">
         <v>163</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="53">
         <v>164</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="53">
         <v>165</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="53">
         <v>166</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="53">
         <v>167</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="53">
         <v>168</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="53">
         <v>169</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="53">
         <v>170</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="53">
         <v>171</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="53">
         <v>172</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="53">
         <v>173</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="53">
         <v>174</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="53">
         <v>175</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="53">
         <v>176</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="53">
         <v>177</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="53">
         <v>178</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="53">
         <v>179</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="53">
         <v>180</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="53">
         <v>181</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="53">
         <v>182</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="53">
         <v>183</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="53">
         <v>184</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="53">
         <v>185</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="53">
         <v>186</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="53">
         <v>187</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="53">
         <v>188</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="53">
         <v>189</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="53">
         <v>190</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="53">
         <v>191</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="53">
         <v>192</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="53">
         <v>193</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="53">
         <v>194</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="53">
         <v>195</v>
       </c>
@@ -8861,7 +8861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="53">
         <v>196</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="53">
         <v>197</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="53">
         <v>198</v>
       </c>
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="53">
         <v>199</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="53">
         <v>200</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="53">
         <v>201</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="53">
         <v>202</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="53">
         <v>203</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="53">
         <v>204</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="53">
         <v>205</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="53">
         <v>206</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="53">
         <v>207</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="53">
         <v>208</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="53">
         <v>209</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="53">
         <v>210</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="53">
         <v>211</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="53">
         <v>212</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="53">
         <v>213</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="53">
         <v>214</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="53">
         <v>215</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="53">
         <v>216</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="53">
         <v>217</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="53">
         <v>218</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="53">
         <v>219</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="53">
         <v>220</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="53">
         <v>221</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="53">
         <v>222</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="53">
         <v>223</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="53">
         <v>224</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="53">
         <v>225</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="53">
         <v>226</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="53">
         <v>227</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="53">
         <v>228</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="53">
         <v>229</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="53">
         <v>230</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="53">
         <v>231</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="53">
         <v>232</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="53">
         <v>233</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="53">
         <v>234</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="53">
         <v>235</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="53">
         <v>236</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="53">
         <v>237</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="53">
         <v>238</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="53">
         <v>239</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="53">
         <v>240</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="53">
         <v>241</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="53">
         <v>242</v>
       </c>
@@ -10083,7 +10083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="53">
         <v>243</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="53">
         <v>244</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="53">
         <v>245</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="53">
         <v>246</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="53">
         <v>247</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="53">
         <v>248</v>
       </c>
@@ -10239,7 +10239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="53">
         <v>249</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="53">
         <v>250</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="53">
         <v>251</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="53">
         <v>252</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="53">
         <v>253</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="53">
         <v>254</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="53">
         <v>255</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="53">
         <v>256</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="53">
         <v>257</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="53">
         <v>258</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="53">
         <v>259</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="53">
         <v>260</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="53">
         <v>261</v>
       </c>
@@ -10577,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="53">
         <v>262</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="53">
         <v>263</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="53">
         <v>264</v>
       </c>
@@ -10655,7 +10655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="53">
         <v>265</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="53">
         <v>266</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="53">
         <v>267</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="53">
         <v>268</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="53">
         <v>269</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="53">
         <v>270</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="53">
         <v>271</v>
       </c>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="53">
         <v>272</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="53">
         <v>273</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="53">
         <v>274</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="53">
         <v>275</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="53">
         <v>276</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="53">
         <v>277</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" s="53">
         <v>278</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="53">
         <v>279</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="53">
         <v>280</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="53">
         <v>281</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="53">
         <v>282</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="53">
         <v>283</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="53">
         <v>284</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="53">
         <v>285</v>
       </c>
@@ -11201,7 +11201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="53">
         <v>286</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="53">
         <v>287</v>
       </c>
@@ -11253,10 +11253,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="53"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="46"/>
       <c r="B292" s="47"/>
       <c r="C292" s="47"/>
@@ -11264,7 +11264,7 @@
       <c r="G292" s="49"/>
       <c r="H292" s="50"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="31"/>
       <c r="B293" s="10"/>
       <c r="C293" s="10"/>
@@ -11272,7 +11272,7 @@
       <c r="G293" s="41"/>
       <c r="H293" s="9"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="38"/>
       <c r="B294" s="10"/>
       <c r="C294" s="10"/>
@@ -11280,7 +11280,7 @@
       <c r="G294" s="41"/>
       <c r="H294" s="9"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="11"/>
       <c r="B295" s="10"/>
       <c r="C295" s="10"/>
@@ -11288,7 +11288,7 @@
       <c r="G295" s="41"/>
       <c r="H295" s="9"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="11"/>
       <c r="B296" s="10"/>
       <c r="C296" s="10"/>
@@ -11296,7 +11296,7 @@
       <c r="G296" s="41"/>
       <c r="H296" s="9"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="11"/>
       <c r="B297" s="10"/>
       <c r="C297" s="10"/>
@@ -11304,7 +11304,7 @@
       <c r="G297" s="41"/>
       <c r="H297" s="9"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="31"/>
       <c r="B298" s="10"/>
       <c r="C298" s="10"/>
@@ -11312,7 +11312,7 @@
       <c r="G298" s="41"/>
       <c r="H298" s="9"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="38"/>
       <c r="B299" s="10"/>
       <c r="C299" s="10"/>
@@ -11320,7 +11320,7 @@
       <c r="G299" s="41"/>
       <c r="H299" s="9"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="11"/>
       <c r="B300" s="10"/>
       <c r="C300" s="10"/>
@@ -11328,7 +11328,7 @@
       <c r="G300" s="41"/>
       <c r="H300" s="9"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="11"/>
       <c r="B301" s="10"/>
       <c r="C301" s="10"/>
@@ -11336,7 +11336,7 @@
       <c r="G301" s="41"/>
       <c r="H301" s="9"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="11"/>
       <c r="B302" s="10"/>
       <c r="C302" s="10"/>
@@ -11344,7 +11344,7 @@
       <c r="G302" s="41"/>
       <c r="H302" s="9"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="31"/>
       <c r="B303" s="10"/>
       <c r="C303" s="10"/>
@@ -11352,7 +11352,7 @@
       <c r="G303" s="41"/>
       <c r="H303" s="9"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="38"/>
       <c r="B304" s="10"/>
       <c r="C304" s="10"/>
@@ -11360,7 +11360,7 @@
       <c r="G304" s="41"/>
       <c r="H304" s="9"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="11"/>
       <c r="B305" s="10"/>
       <c r="C305" s="10"/>
@@ -11368,7 +11368,7 @@
       <c r="G305" s="41"/>
       <c r="H305" s="9"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="11"/>
       <c r="B306" s="10"/>
       <c r="C306" s="10"/>
@@ -11376,7 +11376,7 @@
       <c r="G306" s="41"/>
       <c r="H306" s="9"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="11"/>
       <c r="B307" s="10"/>
       <c r="C307" s="10"/>
@@ -11384,7 +11384,7 @@
       <c r="G307" s="41"/>
       <c r="H307" s="9"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="31"/>
       <c r="B308" s="10"/>
       <c r="C308" s="10"/>
@@ -11392,7 +11392,7 @@
       <c r="G308" s="41"/>
       <c r="H308" s="9"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="38"/>
       <c r="B309" s="10"/>
       <c r="C309" s="10"/>
@@ -11400,7 +11400,7 @@
       <c r="G309" s="41"/>
       <c r="H309" s="9"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="11"/>
       <c r="B310" s="10"/>
       <c r="C310" s="10"/>
@@ -11408,7 +11408,7 @@
       <c r="G310" s="41"/>
       <c r="H310" s="9"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="11"/>
       <c r="B311" s="10"/>
       <c r="C311" s="10"/>
@@ -11416,7 +11416,7 @@
       <c r="G311" s="41"/>
       <c r="H311" s="9"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="11"/>
       <c r="B312" s="10"/>
       <c r="C312" s="10"/>
@@ -11424,7 +11424,7 @@
       <c r="G312" s="41"/>
       <c r="H312" s="9"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="31"/>
       <c r="B313" s="10"/>
       <c r="C313" s="10"/>
@@ -11432,7 +11432,7 @@
       <c r="G313" s="41"/>
       <c r="H313" s="9"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="38"/>
       <c r="B314" s="10"/>
       <c r="C314" s="10"/>
@@ -11440,7 +11440,7 @@
       <c r="G314" s="41"/>
       <c r="H314" s="9"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="11"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10"/>
@@ -11448,7 +11448,7 @@
       <c r="G315" s="41"/>
       <c r="H315" s="9"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="11"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10"/>
@@ -11456,7 +11456,7 @@
       <c r="G316" s="41"/>
       <c r="H316" s="9"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="11"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10"/>
@@ -11464,7 +11464,7 @@
       <c r="G317" s="41"/>
       <c r="H317" s="9"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="31"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10"/>
@@ -11472,7 +11472,7 @@
       <c r="G318" s="41"/>
       <c r="H318" s="9"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="38"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10"/>
@@ -11480,7 +11480,7 @@
       <c r="G319" s="41"/>
       <c r="H319" s="9"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="11"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -11488,7 +11488,7 @@
       <c r="G320" s="41"/>
       <c r="H320" s="9"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="11"/>
       <c r="B321" s="10"/>
       <c r="C321" s="10"/>
@@ -11496,7 +11496,7 @@
       <c r="G321" s="41"/>
       <c r="H321" s="9"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="11"/>
       <c r="B322" s="10"/>
       <c r="C322" s="10"/>
@@ -11504,7 +11504,7 @@
       <c r="G322" s="41"/>
       <c r="H322" s="9"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="31"/>
       <c r="B323" s="10"/>
       <c r="C323" s="10"/>
@@ -11512,7 +11512,7 @@
       <c r="G323" s="41"/>
       <c r="H323" s="9"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="38"/>
       <c r="B324" s="10"/>
       <c r="C324" s="10"/>
@@ -11520,7 +11520,7 @@
       <c r="G324" s="41"/>
       <c r="H324" s="9"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="11"/>
       <c r="B325" s="10"/>
       <c r="C325" s="10"/>
@@ -11528,7 +11528,7 @@
       <c r="G325" s="41"/>
       <c r="H325" s="9"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="11"/>
       <c r="B326" s="10"/>
       <c r="C326" s="10"/>
@@ -11536,7 +11536,7 @@
       <c r="G326" s="41"/>
       <c r="H326" s="9"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="11"/>
       <c r="B327" s="10"/>
       <c r="C327" s="10"/>
@@ -11544,7 +11544,7 @@
       <c r="G327" s="41"/>
       <c r="H327" s="9"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="31"/>
       <c r="B328" s="10"/>
       <c r="C328" s="10"/>
@@ -11552,7 +11552,7 @@
       <c r="G328" s="41"/>
       <c r="H328" s="9"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="38"/>
       <c r="B329" s="10"/>
       <c r="C329" s="10"/>
@@ -11560,7 +11560,7 @@
       <c r="G329" s="41"/>
       <c r="H329" s="9"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="11"/>
       <c r="B330" s="10"/>
       <c r="C330" s="10"/>
@@ -11568,7 +11568,7 @@
       <c r="G330" s="41"/>
       <c r="H330" s="9"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="11"/>
       <c r="B331" s="10"/>
       <c r="C331" s="10"/>
@@ -11576,7 +11576,7 @@
       <c r="G331" s="41"/>
       <c r="H331" s="9"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="11"/>
       <c r="B332" s="10"/>
       <c r="C332" s="10"/>
@@ -11584,7 +11584,7 @@
       <c r="G332" s="41"/>
       <c r="H332" s="9"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="31"/>
       <c r="B333" s="10"/>
       <c r="C333" s="10"/>
@@ -11592,7 +11592,7 @@
       <c r="G333" s="41"/>
       <c r="H333" s="9"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="38"/>
       <c r="B334" s="10"/>
       <c r="C334" s="10"/>
@@ -11600,7 +11600,7 @@
       <c r="G334" s="41"/>
       <c r="H334" s="9"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="11"/>
       <c r="B335" s="10"/>
       <c r="C335" s="10"/>
@@ -11608,7 +11608,7 @@
       <c r="G335" s="41"/>
       <c r="H335" s="9"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="11"/>
       <c r="B336" s="10"/>
       <c r="C336" s="10"/>
@@ -11616,7 +11616,7 @@
       <c r="G336" s="41"/>
       <c r="H336" s="9"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="11"/>
       <c r="B337" s="10"/>
       <c r="C337" s="10"/>
@@ -11624,7 +11624,7 @@
       <c r="G337" s="41"/>
       <c r="H337" s="9"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="31"/>
       <c r="B338" s="10"/>
       <c r="C338" s="10"/>
@@ -11632,7 +11632,7 @@
       <c r="G338" s="41"/>
       <c r="H338" s="9"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="38"/>
       <c r="B339" s="10"/>
       <c r="C339" s="10"/>
@@ -11640,7 +11640,7 @@
       <c r="G339" s="41"/>
       <c r="H339" s="9"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="11"/>
       <c r="B340" s="10"/>
       <c r="C340" s="10"/>
@@ -11648,7 +11648,7 @@
       <c r="G340" s="41"/>
       <c r="H340" s="9"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="11"/>
       <c r="B341" s="10"/>
       <c r="C341" s="10"/>
@@ -11656,7 +11656,7 @@
       <c r="G341" s="41"/>
       <c r="H341" s="9"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" s="11"/>
       <c r="B342" s="10"/>
       <c r="C342" s="10"/>
@@ -11664,7 +11664,7 @@
       <c r="G342" s="41"/>
       <c r="H342" s="9"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" s="31"/>
       <c r="B343" s="10"/>
       <c r="C343" s="10"/>
@@ -11672,7 +11672,7 @@
       <c r="G343" s="41"/>
       <c r="H343" s="9"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" s="38"/>
       <c r="B344" s="10"/>
       <c r="C344" s="10"/>
@@ -11680,7 +11680,7 @@
       <c r="G344" s="41"/>
       <c r="H344" s="9"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="11"/>
       <c r="B345" s="10"/>
       <c r="C345" s="10"/>
@@ -11688,7 +11688,7 @@
       <c r="G345" s="41"/>
       <c r="H345" s="9"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" s="11"/>
       <c r="B346" s="10"/>
       <c r="C346" s="10"/>
@@ -11708,14 +11708,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
